--- a/output/pdf_financials_xlsx/MYID.xlsx
+++ b/output/pdf_financials_xlsx/MYID.xlsx
@@ -868,7 +868,7 @@
         <v>3.819196</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.253621</v>
+        <v>4.848318</v>
       </c>
     </row>
     <row r="11">
@@ -917,7 +917,7 @@
         <v>0.338423</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2.657053</v>
+        <v>-0.937644</v>
       </c>
     </row>
     <row r="12">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.011538</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.053006</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -954,19 +954,19 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.010657</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001693</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000382</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002269</v>
       </c>
     </row>
     <row r="13">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.39062</v>
+        <v>-0.402158</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.623969</v>
+        <v>-0.676975</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1735,19 +1735,19 @@
         <v>-9.055149999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.323322</v>
+        <v>-6.333979</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.190509</v>
+        <v>-4.192202</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.909732</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.388332</v>
+        <v>0.38795</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.033852</v>
+        <v>-1.036121</v>
       </c>
     </row>
     <row r="28">
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.39062</v>
+        <v>-0.402158</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.623969</v>
+        <v>-0.676975</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1833,19 +1833,19 @@
         <v>-9.055149999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.323322</v>
+        <v>-6.333979</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.190509</v>
+        <v>-4.192202</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.909732</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.388332</v>
+        <v>0.38795</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.033852</v>
+        <v>-1.036121</v>
       </c>
     </row>
     <row r="30">
@@ -1886,19 +1886,19 @@
         <v>-262.0365531319143</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-632.2057588482304</v>
+        <v>-633.2712457508499</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-177.4804646966893</v>
+        <v>-177.5521682598439</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>22.12422545439158</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>7.644761102692002</v>
+        <v>7.637240994276449</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-20.70992736465507</v>
+        <v>-20.75537954271383</v>
       </c>
     </row>
     <row r="31">
@@ -2047,10 +2047,10 @@
         <v>0.164279</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.587717</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.472296</v>
       </c>
     </row>
     <row r="35">
@@ -2133,10 +2133,10 @@
         <v>0.164279</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.587717</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.472296</v>
       </c>
     </row>
     <row r="37">
@@ -2649,10 +2649,10 @@
         <v>0.066882</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.633646</v>
+        <v>0.045929</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.511636</v>
+        <v>0.03934</v>
       </c>
     </row>
     <row r="49">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -24084,7 +24084,11 @@
           <t>Refund of environmental reclamation deposit</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -26480,7 +26484,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -26710,7 +26714,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -28146,7 +28150,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -32460,7 +32464,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E346" s="5" t="n">

--- a/output/pdf_financials_xlsx/MYID.xlsx
+++ b/output/pdf_financials_xlsx/MYID.xlsx
@@ -1784,19 +1784,19 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.023785</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.018453</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.019829</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.014741</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.014419</v>
       </c>
     </row>
     <row r="29">
@@ -1833,19 +1833,19 @@
         <v>-9.055149999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.333979</v>
+        <v>-6.310194</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.192202</v>
+        <v>-4.173749</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.909732</v>
+        <v>0.929561</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.38795</v>
+        <v>0.402691</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.036121</v>
+        <v>-1.021702</v>
       </c>
     </row>
     <row r="30">
@@ -1886,19 +1886,19 @@
         <v>-262.0365531319143</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-633.2712457508499</v>
+        <v>-630.8932213557289</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-177.5521682598439</v>
+        <v>-176.7706290685313</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>22.12422545439158</v>
+        <v>22.60645677805078</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>7.637240994276449</v>
+        <v>7.927434497296501</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-20.75537954271383</v>
+        <v>-20.46654086689663</v>
       </c>
     </row>
     <row r="31">
@@ -4896,19 +4896,19 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.023785</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.018453</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.019829</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.014741</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.014419</v>
       </c>
     </row>
     <row r="101">
@@ -18034,7 +18034,11 @@
           <t>Depreciation of property and equipment 4</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -19472,7 +19476,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -21270,7 +21278,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MYID.xlsx
+++ b/output/pdf_financials_xlsx/MYID.xlsx
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.137395</v>
+        <v>0.180332</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.171115</v>
+        <v>0.196018</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.228587</v>
+        <v>0.271524</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.205232</v>
+        <v>0.230135</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.228587</v>
+        <v>-0.271524</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.205232</v>
+        <v>-0.230135</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.086226</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0.833163</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.236063</v>
+        <v>1.322289</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.351865</v>
@@ -2637,7 +2637,7 @@
         <v>0.290208</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.236657</v>
+        <v>0.150431</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.211487</v>
@@ -5148,25 +5148,25 @@
         <v>-0.012645</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.003616</v>
+        <v>0.111458</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.233476</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.621452</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.444333</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-1.428474</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-0.653426</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>0.19745</v>
       </c>
     </row>
     <row r="107">
@@ -5326,19 +5326,19 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.010657</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.26547</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.332294</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.252712</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.088562</v>
       </c>
     </row>
     <row r="111">
@@ -5825,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.017574</v>
       </c>
     </row>
     <row r="122">
@@ -18112,7 +18112,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -18412,7 +18416,11 @@
           <t>Net change in non-cash operating working capital 14</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -18486,7 +18494,11 @@
           <t>Shares issued for debt settlement, and repurchase of shares 9</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -19402,7 +19414,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -19628,7 +19644,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -19852,7 +19872,11 @@
           <t>Net change in non-cash operating working capital 17</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -22204,7 +22228,11 @@
           <t>Net change in non-cash operating working capital 22</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -32168,7 +32196,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E342" s="5" t="n">
         <v>0.042937</v>
       </c>
